--- a/templates/08_mame_evolvepro_raw.xlsx
+++ b/templates/08_mame_evolvepro_raw.xlsx
@@ -441,37 +441,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Q232A</t>
+          <t>65A</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.85</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Y233A</t>
+          <t>203Y</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.48</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A40P</t>
+          <t>65T</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.33</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E61Y</t>
+          <t>64L</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -481,7 +481,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L150V</t>
+          <t>206K</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -491,11 +491,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A40P_E61Y</t>
+          <t>66H</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.11</v>
+        <v>0.48</v>
       </c>
     </row>
   </sheetData>
